--- a/nomerTelpon/NomerTelpon.xlsx
+++ b/nomerTelpon/NomerTelpon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\reunusa\nomerTelpon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BDD773D-771F-4EA3-9215-029B2A44F8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4CF4BB-DF0C-41C7-818E-F4340C7A6F77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE39D515-3E0E-40C4-AEA7-E73322AD3B85}"/>
   </bookViews>
@@ -86,42 +86,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -139,24 +109,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFDDDDDD"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFDDDDDD"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFDDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -164,22 +121,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -516,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACBF427B-C02F-459F-B4C0-0628669CFFE8}">
-  <dimension ref="A1:B145"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="2" customWidth="1"/>
@@ -524,467 +472,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7">
-        <v>6281323285482</v>
+      <c r="B2" s="4">
+        <v>6281434343433</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>6285759677386</v>
+      <c r="B3" s="4">
+        <v>6285743434334</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="7"/>
-    </row>
-    <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-    </row>
-    <row r="18" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-    </row>
-    <row r="20" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-    </row>
-    <row r="21" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-    </row>
-    <row r="23" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-    </row>
-    <row r="24" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-    </row>
-    <row r="25" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-    </row>
-    <row r="26" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-    </row>
-    <row r="27" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-    </row>
-    <row r="28" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
-    </row>
-    <row r="29" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-    </row>
-    <row r="30" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-    </row>
-    <row r="31" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-    </row>
-    <row r="32" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
-    </row>
-    <row r="45" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
-    </row>
-    <row r="46" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
-    </row>
-    <row r="47" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
-    </row>
-    <row r="48" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="3"/>
-    </row>
-    <row r="51" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
-    </row>
-    <row r="52" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="3"/>
-    </row>
-    <row r="54" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="3"/>
-    </row>
-    <row r="55" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
-    </row>
-    <row r="62" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
-    </row>
-    <row r="64" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3"/>
-    </row>
-    <row r="67" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3"/>
-    </row>
-    <row r="68" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3"/>
-    </row>
-    <row r="69" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3"/>
-    </row>
-    <row r="70" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3"/>
-    </row>
-    <row r="71" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3"/>
-    </row>
-    <row r="72" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3"/>
-    </row>
-    <row r="73" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3"/>
-    </row>
-    <row r="74" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-    </row>
-    <row r="75" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3"/>
-    </row>
-    <row r="76" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
-    </row>
-    <row r="77" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
-    </row>
-    <row r="78" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3"/>
-    </row>
-    <row r="79" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
-    </row>
-    <row r="80" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-    </row>
-    <row r="81" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-    </row>
-    <row r="82" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
-    </row>
-    <row r="83" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
-    </row>
-    <row r="84" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
-    </row>
-    <row r="85" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
-    </row>
-    <row r="86" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3"/>
-    </row>
-    <row r="87" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3"/>
-    </row>
-    <row r="88" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3"/>
-    </row>
-    <row r="89" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
-    </row>
-    <row r="90" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3"/>
-    </row>
-    <row r="91" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3"/>
-    </row>
-    <row r="92" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3"/>
-    </row>
-    <row r="93" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="3"/>
-    </row>
-    <row r="94" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3"/>
-    </row>
-    <row r="95" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
-    </row>
-    <row r="96" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
-    </row>
-    <row r="97" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
-    </row>
-    <row r="98" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
-    </row>
-    <row r="99" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
-    </row>
-    <row r="100" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
-    </row>
-    <row r="101" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
-    </row>
-    <row r="102" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
-    </row>
-    <row r="103" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
-    </row>
-    <row r="104" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
-    </row>
-    <row r="105" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-    </row>
-    <row r="106" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-    </row>
-    <row r="107" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-    </row>
-    <row r="108" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
-    </row>
-    <row r="109" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
-    </row>
-    <row r="110" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
-    </row>
-    <row r="111" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
-    </row>
-    <row r="112" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
-    </row>
-    <row r="113" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
-    </row>
-    <row r="114" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
-    </row>
-    <row r="115" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
-    </row>
-    <row r="116" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
-    </row>
-    <row r="117" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
-    </row>
-    <row r="118" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
-    </row>
-    <row r="119" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
-    </row>
-    <row r="120" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="4"/>
-    </row>
-    <row r="121" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
-    </row>
-    <row r="122" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
-    </row>
-    <row r="123" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="3"/>
-    </row>
-    <row r="124" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="3"/>
-    </row>
-    <row r="125" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
-    </row>
-    <row r="126" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="4"/>
-    </row>
-    <row r="127" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
-    </row>
-    <row r="128" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="3"/>
-    </row>
-    <row r="129" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="3"/>
-    </row>
-    <row r="130" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="3"/>
-    </row>
-    <row r="131" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="3"/>
-    </row>
-    <row r="132" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
-    </row>
-    <row r="133" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3"/>
-    </row>
-    <row r="134" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="3"/>
-    </row>
-    <row r="135" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="3"/>
-    </row>
-    <row r="136" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="3"/>
-    </row>
-    <row r="137" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="3"/>
-    </row>
-    <row r="138" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="3"/>
-    </row>
-    <row r="139" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="3"/>
-    </row>
-    <row r="140" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="3"/>
-    </row>
-    <row r="141" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="3"/>
-    </row>
-    <row r="142" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
-    </row>
-    <row r="143" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="3"/>
-    </row>
-    <row r="144" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="3"/>
-    </row>
-    <row r="145" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="3"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
